--- a/data/vendor-search/results_all_smartspeakers.xlsx
+++ b/data/vendor-search/results_all_smartspeakers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>9.1</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:h:bose:soundtouch_30:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bose soundtouch</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>3.3</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -516,6 +530,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:amazon:echo_show_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_show:-:*:*:*:*:*:*:*|cpe:2.3:o:amazon:echo_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:amazon:echo_dot_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:-:*:*:*:*:*:*:*|cpe:2.3:o:amazon:echo_spot_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_spot:-:*:*:*:*:*:*:*|cpe:2.3:o:amazon:echo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>amazon echo</t>
         </is>
       </c>
     </row>
@@ -538,8 +557,10 @@
       <c r="D4" t="n">
         <v>4.3</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,6 +570,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:google:chromecast_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:google:chromecast:-:*:*:*:*:*:*:*|cpe:2.3:o:google:home_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:google:home:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>google home</t>
         </is>
       </c>
     </row>
@@ -571,8 +597,10 @@
       <c r="D5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -582,6 +610,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:mediatek:mt8163_firmware:-:*:*:*:*:android:*:*|cpe:2.3:h:mediatek:mt8163:-:*:*:*:*:android:*:*|cpe:2.3:o:mediatek:mt6625_firmware:-:*:*:*:*:android:*:*|cpe:2.3:h:mediatek:mt6625:-:*:*:*:*:android:*:*|cpe:2.3:o:mediatek:mt6577_firmware:-:*:*:*:*:android:*:*|cpe:2.3:h:mediatek:mt6577:-:*:*:*:*:android:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>amazon echo|echo dot</t>
         </is>
       </c>
     </row>
@@ -604,8 +637,10 @@
       <c r="D6" t="n">
         <v>6.8</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -615,6 +650,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:one_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -637,8 +677,10 @@
       <c r="D7" t="n">
         <v>7.6</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -646,6 +688,11 @@
           <t>cpe:2.3:o:amazon:alexa:8960323972:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:-:*:2nd_gen:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:-:*:3rd_gen:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>amazon alexa|echo dot</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,8 +714,10 @@
       <c r="D8" t="n">
         <v>4.3</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -678,6 +727,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_100_firmware:15.9:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_100:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -701,8 +755,10 @@
       <c r="D9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -712,6 +768,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_100_firmware:15.9:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_100:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -735,8 +796,10 @@
       <c r="D10" t="n">
         <v>6.5</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -746,6 +809,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_100_firmware:15.9:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_100:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -769,8 +837,10 @@
       <c r="D11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -780,6 +850,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_100_firmware:15.9:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_100:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -803,8 +878,10 @@
       <c r="D12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -814,6 +891,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_300:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -837,8 +919,10 @@
       <c r="D13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E13" t="n">
-        <v>3</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -848,6 +932,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_300:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -871,8 +960,10 @@
       <c r="D14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E14" t="n">
-        <v>3</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -882,6 +973,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_300:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -904,8 +1000,10 @@
       <c r="D15" t="n">
         <v>5.4</v>
       </c>
-      <c r="E15" t="n">
-        <v>3</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -915,6 +1013,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:a:bose:soundtouch:-:*:*:*:*:android:*:*|cpe:2.3:a:bose:soundtouch:-:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bose soundtouch</t>
         </is>
       </c>
     </row>
@@ -937,8 +1040,10 @@
       <c r="D16" t="n">
         <v>5.4</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -948,6 +1053,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:a:bose:soundtouch:-:*:*:*:*:android:*:*|cpe:2.3:a:bose:soundtouch:-:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bose soundtouch</t>
         </is>
       </c>
     </row>
@@ -970,8 +1080,10 @@
       <c r="D17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E17" t="n">
-        <v>3</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -979,6 +1091,11 @@
           <t>cpe:2.3:a:bose:soundtouch:-:*:*:*:*:android:*:*|cpe:2.3:a:bose:soundtouch:-:*:*:*:*:iphone_os:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bose soundtouch</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,8 +1116,10 @@
       <c r="D18" t="n">
         <v>6.4</v>
       </c>
-      <c r="E18" t="n">
-        <v>3</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -1008,6 +1127,11 @@
           <t>cpe:2.3:a:lenovo:smart_assistant:*:*:*:*:*:android:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>amazon alexa</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1028,8 +1152,10 @@
       <c r="D19" t="n">
         <v>6.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>3</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,6 +1165,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:a:bose:soundtouch:18.1.4:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bose soundtouch</t>
         </is>
       </c>
     </row>
@@ -1061,8 +1192,10 @@
       <c r="D20" t="n">
         <v>4.2</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -1070,6 +1203,11 @@
           <t>cpe:2.3:o:amazon:echo_dot_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>amazon echo|echo dot</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1090,8 +1228,10 @@
       <c r="D21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1101,6 +1241,11 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1123,8 +1268,10 @@
       <c r="D22" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E22" t="n">
-        <v>3.1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1134,6 +1281,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1156,8 +1308,10 @@
       <c r="D23" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E23" t="n">
-        <v>3.1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -1165,6 +1319,11 @@
           <t>cpe:2.3:o:amazon:echo_dot_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:3.0:*:*:*:*:*:*:*|cpe:2.3:h:amazon:echo_dot:4.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>amazon echo|echo dot</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1185,8 +1344,10 @@
       <c r="D24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.1</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1196,6 +1357,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:one_firmware:70.3-35220:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1218,8 +1384,10 @@
       <c r="D25" t="n">
         <v>6.5</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.1</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1229,6 +1397,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:one_firmware:70.3-35220:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1251,8 +1424,10 @@
       <c r="D26" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1262,6 +1437,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:one_firmware:70.3-35220:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1284,8 +1464,10 @@
       <c r="D27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1295,6 +1477,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:one_firmware:70.3-35220:*:*:*:*:*:*:*|cpe:2.3:h:sonos:one:-:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s1:*:*:*:*:*:*:*:*|cpe:2.3:a:sonos:s2:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>sonos one</t>
         </is>
       </c>
     </row>
@@ -1317,8 +1504,10 @@
       <c r="D28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1328,6 +1517,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>cpe:2.3:o:lenovo:smart_clock_essential_with_alexa_built_in_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:smart_clock_essential_with_alexa_built_in:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>lenovo smart clock</t>
         </is>
       </c>
     </row>
@@ -1351,8 +1545,10 @@
       <c r="D29" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1362,6 +1558,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:o:google:nest_audio_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:google:nest_audio:-:*:*:*:*:*:*:*|cpe:2.3:o:google:nest_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:google:nest_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:google:home_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:google:home_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:google:home_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:google:home:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>google home</t>
         </is>
       </c>
     </row>
@@ -1385,8 +1586,10 @@
       <c r="D30" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E30" t="n">
-        <v>3</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1396,6 +1599,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_300_firmware:81.1-58074:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_300:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
@@ -1418,8 +1626,10 @@
       <c r="D31" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1429,6 +1639,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>cpe:2.3:a:tuya:smartlife:6.3.1:*:*:*:*:iphone_os:*:*|cpe:2.3:a:tuya:smartlife:6.3.4:*:*:*:*:android:*:*|cpe:2.3:a:tuya:tuya:*:*:*:*:*:android:*:*|cpe:2.3:a:tuya:tuya:*:*:*:*:*:iphone_os:*:*|cpe:2.3:a:tuya:tuya_smart:6.3.1:*:*:*:*:android:*:*|cpe:2.3:a:tuya:tuya_smart:6.3.1:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>amazon alexa</t>
         </is>
       </c>
     </row>
@@ -1452,8 +1667,10 @@
       <c r="D32" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E32" t="n">
-        <v>3.1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1463,6 +1680,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonos:era_300_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sonos:era_300:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>sonos era</t>
         </is>
       </c>
     </row>
